--- a/signal/validation/paragraphs_to_label.xlsx
+++ b/signal/validation/paragraphs_to_label.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rayyaankazi/Desktop/Masters-Project/signal/validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F30A48F5-9CB0-0B44-A1E1-3360C5EFC394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AA6033-8104-B049-B235-5731782F0AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13320" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="160">
   <si>
     <t>HUMAN VALIDATION — FISCAL STANCE LABELING</t>
   </si>
@@ -309,6 +309,198 @@
   </si>
   <si>
     <t>De hecho, en el discurso de recién mencionó mi querido amigo Santiago Abascal al pichón de tirano que tienen en España. Si a esto le sumamos la cuestión migratoria, que lo que hace es aumentar indiscriminadamente la cantidad de receptores de pedazos de la torta sin ninguna exigencia de aporte de ningún tipo, se termina estafando a la población que pagó impuestos durante tantos años, devolviéndoles un sistema camino al colapso.</t>
+  </si>
+  <si>
+    <t>Dije que el riesgo país está cayendo y que ahora Argentina es solvente, muestra de confidanzia en la posición fiscal.</t>
+  </si>
+  <si>
+    <t>Habla sobre reducir el deficit</t>
+  </si>
+  <si>
+    <t>Habla sobre policías fiscales expansionarias</t>
+  </si>
+  <si>
+    <t>Habla sobre la obra pública</t>
+  </si>
+  <si>
+    <t>Argentina está bajando la inflación, una posición fuerte</t>
+  </si>
+  <si>
+    <t>habla sobre el equilibiro fiscal</t>
+  </si>
+  <si>
+    <t>deficit cero</t>
+  </si>
+  <si>
+    <t>Sentimiento dovish, habla sobre crear trabajos y la pandemia</t>
+  </si>
+  <si>
+    <t>La lucha para eliminar la inflación</t>
+  </si>
+  <si>
+    <t>No es tan claro</t>
+  </si>
+  <si>
+    <t>Quiere reducir el involucramiento del estado</t>
+  </si>
+  <si>
+    <t>Habla sobre el gasto publico pero no es tan claro</t>
+  </si>
+  <si>
+    <t>Habla sobre la situación pobre en Argentina, puede que sea nuetral?</t>
+  </si>
+  <si>
+    <t>Algo general</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Quiere que el banco central tenga menos involucramiento en la economía</t>
+  </si>
+  <si>
+    <t>Habla de manera positiva sobre la obra publica</t>
+  </si>
+  <si>
+    <t>Sentimiento anti mercado</t>
+  </si>
+  <si>
+    <t>Ayuda a los jubilados</t>
+  </si>
+  <si>
+    <t>Habla sobre obra publica</t>
+  </si>
+  <si>
+    <t>Reducir la pobreza, pero no es claro si es dovish o hawkish</t>
+  </si>
+  <si>
+    <t>Quiere reducir la deuda</t>
+  </si>
+  <si>
+    <t>Habla mal sobre otros presidentes pero no es hawkish ni dovish</t>
+  </si>
+  <si>
+    <t>Inversión social</t>
+  </si>
+  <si>
+    <t>Habla sobre el mal estado de la economía</t>
+  </si>
+  <si>
+    <t>Habla sobre los subsidios</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>Habla sobre medidas para eliminar la pobreza</t>
+  </si>
+  <si>
+    <t>Muy hawkish, habla sobre el crecimiento economíca y reducir el gasto publico</t>
+  </si>
+  <si>
+    <t>Critica las economistas pero habla que han reducido la inflacion</t>
+  </si>
+  <si>
+    <t>Muy hawkish</t>
+  </si>
+  <si>
+    <t>Quiere mejorar la productividad</t>
+  </si>
+  <si>
+    <t>ajuste fiscal</t>
+  </si>
+  <si>
+    <t>habla sobre las situaciones dificiles</t>
+  </si>
+  <si>
+    <t>balancia fiscal</t>
+  </si>
+  <si>
+    <t>Quiere reducir productos importados puede que sea neutral</t>
+  </si>
+  <si>
+    <t>Anti privatizacion</t>
+  </si>
+  <si>
+    <t>obra publica</t>
+  </si>
+  <si>
+    <t>habla sobre control del estado</t>
+  </si>
+  <si>
+    <t>elimnó el deficit</t>
+  </si>
+  <si>
+    <t>comentario general</t>
+  </si>
+  <si>
+    <t>reducio el deficit</t>
+  </si>
+  <si>
+    <t>dovish</t>
+  </si>
+  <si>
+    <t>elogia el capitalismo</t>
+  </si>
+  <si>
+    <t>no es claro</t>
+  </si>
+  <si>
+    <t>general puede que sea hawkish</t>
+  </si>
+  <si>
+    <t>no es claro, quizas dovish</t>
+  </si>
+  <si>
+    <t>justicia social</t>
+  </si>
+  <si>
+    <t>habla negativamente sobre la situacion actual</t>
+  </si>
+  <si>
+    <t>Policia para los jubilados</t>
+  </si>
+  <si>
+    <t>los juegos olimpicos no es relevante</t>
+  </si>
+  <si>
+    <t>sentimiento dovish</t>
+  </si>
+  <si>
+    <t>quiere reducir el debt</t>
+  </si>
+  <si>
+    <t>no super claro</t>
+  </si>
+  <si>
+    <t>discurso general sobre el medio ambiente</t>
+  </si>
+  <si>
+    <t>esceptico del phillips curve</t>
+  </si>
+  <si>
+    <t>nuetral - dijo por periodista asi que es ruido</t>
+  </si>
+  <si>
+    <t>Habla sobre el medio ambiete, la flexibilidad de plazos y tal (puede que sea neutral)</t>
+  </si>
+  <si>
+    <t>habla sobre lograr el equilibiro fiscal</t>
+  </si>
+  <si>
+    <t>Habla sobre mejorar la situación al largo plazo (puede que sea nuetral)</t>
+  </si>
+  <si>
+    <t>deficit cero - claramente hawkish</t>
+  </si>
+  <si>
+    <t>Habla sobre los derechos de propiedad pero es general</t>
+  </si>
+  <si>
+    <t>Quiere apartarse de las organizaciones globales pero no es claramente hawkish</t>
+  </si>
+  <si>
+    <t>Habla contra la privatización</t>
   </si>
 </sst>
 </file>
@@ -382,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -398,14 +590,21 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -839,7 +1038,7 @@
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="85" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="4" max="4" width="30" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
@@ -866,19 +1065,23 @@
       <c r="C2" s="6">
         <v>1</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="5" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="144" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C3" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D3" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="4" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
@@ -888,21 +1091,25 @@
         <v>26</v>
       </c>
       <c r="C4" s="6">
-        <v>1</v>
-      </c>
-      <c r="D4" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="256" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
+      <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="6">
         <v>1</v>
       </c>
-      <c r="D5" s="10"/>
+      <c r="D5" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
@@ -914,19 +1121,23 @@
       <c r="C6" s="6">
         <v>0</v>
       </c>
-      <c r="D6" s="7"/>
+      <c r="D6" s="10" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="80" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
+      <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="6">
         <v>-1</v>
       </c>
-      <c r="D7" s="10"/>
+      <c r="D7" s="9" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
@@ -938,19 +1149,23 @@
       <c r="C8" s="6">
         <v>-1</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="10" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="64" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
+      <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
       </c>
-      <c r="D9" s="10"/>
+      <c r="D9" s="9" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
@@ -962,19 +1177,23 @@
       <c r="C10" s="6">
         <v>0</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="10" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
+      <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="6">
         <v>-1</v>
       </c>
-      <c r="D11" s="10"/>
+      <c r="D11" s="9" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="12" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
@@ -986,19 +1205,23 @@
       <c r="C12" s="6">
         <v>1</v>
       </c>
-      <c r="D12" s="7"/>
+      <c r="D12" s="10" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="96" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
+      <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C13" s="6">
         <v>0</v>
       </c>
-      <c r="D13" s="10"/>
+      <c r="D13" s="9" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="14" spans="1:4" ht="128" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
@@ -1010,19 +1233,23 @@
       <c r="C14" s="6">
         <v>1</v>
       </c>
-      <c r="D14" s="7"/>
+      <c r="D14" s="10" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="240" x14ac:dyDescent="0.2">
-      <c r="A15" s="8">
+      <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="10"/>
+        <v>-1</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="16" spans="1:4" ht="112" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
@@ -1034,19 +1261,23 @@
       <c r="C16" s="6">
         <v>1</v>
       </c>
-      <c r="D16" s="7"/>
+      <c r="D16" s="10" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="17" spans="1:4" ht="96" x14ac:dyDescent="0.2">
-      <c r="A17" s="8">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C17" s="6">
         <v>-1</v>
       </c>
-      <c r="D17" s="10"/>
+      <c r="D17" s="9" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="18" spans="1:4" ht="256" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
@@ -1058,19 +1289,23 @@
       <c r="C18" s="6">
         <v>-1</v>
       </c>
-      <c r="D18" s="7"/>
+      <c r="D18" s="10" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="19" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A19" s="8">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C19" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D19" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="20" spans="1:4" ht="256" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
@@ -1082,19 +1317,23 @@
       <c r="C20" s="6">
         <v>0</v>
       </c>
-      <c r="D20" s="7"/>
+      <c r="D20" s="10" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="21" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A21" s="8">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D21" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="22" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
@@ -1106,19 +1345,23 @@
       <c r="C22" s="6">
         <v>0</v>
       </c>
-      <c r="D22" s="7"/>
+      <c r="D22" s="10" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="23" spans="1:4" ht="80" x14ac:dyDescent="0.2">
-      <c r="A23" s="8">
+      <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C23" s="6">
         <v>0</v>
       </c>
-      <c r="D23" s="10"/>
+      <c r="D23" s="9" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
@@ -1130,19 +1373,23 @@
       <c r="C24" s="6">
         <v>1</v>
       </c>
-      <c r="D24" s="7"/>
+      <c r="D24" s="10" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="25" spans="1:4" ht="96" x14ac:dyDescent="0.2">
-      <c r="A25" s="8">
+      <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="8" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="6">
         <v>-1</v>
       </c>
-      <c r="D25" s="10"/>
+      <c r="D25" s="9" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="26" spans="1:4" ht="192" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
@@ -1154,19 +1401,23 @@
       <c r="C26" s="6">
         <v>-1</v>
       </c>
-      <c r="D26" s="7"/>
+      <c r="D26" s="10" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="27" spans="1:4" ht="96" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
+      <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="8" t="s">
         <v>49</v>
       </c>
       <c r="C27" s="6">
         <v>-1</v>
       </c>
-      <c r="D27" s="10"/>
+      <c r="D27" s="9" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="28" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
@@ -1178,19 +1429,23 @@
       <c r="C28" s="6">
         <v>-1</v>
       </c>
-      <c r="D28" s="7"/>
+      <c r="D28" s="10" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="29" spans="1:4" ht="64" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
+      <c r="A29" s="7">
         <v>28</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="8" t="s">
         <v>51</v>
       </c>
       <c r="C29" s="6">
         <v>0</v>
       </c>
-      <c r="D29" s="10"/>
+      <c r="D29" s="9" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="30" spans="1:4" ht="208" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
@@ -1200,21 +1455,25 @@
         <v>52</v>
       </c>
       <c r="C30" s="6">
-        <v>0</v>
-      </c>
-      <c r="D30" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="31" spans="1:4" ht="128" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
+      <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" s="8" t="s">
         <v>53</v>
       </c>
       <c r="C31" s="6">
         <v>0</v>
       </c>
-      <c r="D31" s="10"/>
+      <c r="D31" s="9" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="32" spans="1:4" ht="208" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
@@ -1226,19 +1485,23 @@
       <c r="C32" s="6">
         <v>-1</v>
       </c>
-      <c r="D32" s="7"/>
+      <c r="D32" s="10" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="33" spans="1:4" ht="80" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
+      <c r="A33" s="7">
         <v>32</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="8" t="s">
         <v>55</v>
       </c>
       <c r="C33" s="6">
-        <v>0</v>
-      </c>
-      <c r="D33" s="10"/>
+        <v>-1</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="34" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
@@ -1250,19 +1513,23 @@
       <c r="C34" s="6">
         <v>-1</v>
       </c>
-      <c r="D34" s="7"/>
+      <c r="D34" s="10" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="35" spans="1:4" ht="80" x14ac:dyDescent="0.2">
-      <c r="A35" s="8">
+      <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="8" t="s">
         <v>57</v>
       </c>
       <c r="C35" s="6">
         <v>0</v>
       </c>
-      <c r="D35" s="10"/>
+      <c r="D35" s="9" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="36" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
@@ -1272,21 +1539,25 @@
         <v>58</v>
       </c>
       <c r="C36" s="6">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="37" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A37" s="8">
+      <c r="A37" s="7">
         <v>36</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="8" t="s">
         <v>59</v>
       </c>
       <c r="C37" s="6">
-        <v>0</v>
-      </c>
-      <c r="D37" s="10"/>
+        <v>-1</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="38" spans="1:4" ht="256" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
@@ -1298,19 +1569,23 @@
       <c r="C38" s="6">
         <v>1</v>
       </c>
-      <c r="D38" s="7"/>
+      <c r="D38" s="10" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="39" spans="1:4" ht="128" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
+      <c r="A39" s="7">
         <v>38</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="8" t="s">
         <v>61</v>
       </c>
       <c r="C39" s="6">
         <v>1</v>
       </c>
-      <c r="D39" s="10"/>
+      <c r="D39" s="9" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="40" spans="1:4" ht="192" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
@@ -1322,19 +1597,23 @@
       <c r="C40" s="6">
         <v>1</v>
       </c>
-      <c r="D40" s="7"/>
+      <c r="D40" s="10" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="41" spans="1:4" ht="144" x14ac:dyDescent="0.2">
-      <c r="A41" s="8">
+      <c r="A41" s="7">
         <v>40</v>
       </c>
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C41" s="6">
-        <v>1</v>
-      </c>
-      <c r="D41" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="42" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
@@ -1346,19 +1625,23 @@
       <c r="C42" s="6">
         <v>1</v>
       </c>
-      <c r="D42" s="7"/>
+      <c r="D42" s="10" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="43" spans="1:4" ht="288" x14ac:dyDescent="0.2">
-      <c r="A43" s="8">
+      <c r="A43" s="7">
         <v>42</v>
       </c>
-      <c r="B43" s="9" t="s">
+      <c r="B43" s="8" t="s">
         <v>65</v>
       </c>
       <c r="C43" s="6">
         <v>-1</v>
       </c>
-      <c r="D43" s="10"/>
+      <c r="D43" s="9" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="44" spans="1:4" ht="160" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
@@ -1370,19 +1653,23 @@
       <c r="C44" s="6">
         <v>1</v>
       </c>
-      <c r="D44" s="7"/>
+      <c r="D44" s="10" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="45" spans="1:4" ht="208" x14ac:dyDescent="0.2">
-      <c r="A45" s="8">
+      <c r="A45" s="7">
         <v>44</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="8" t="s">
         <v>67</v>
       </c>
       <c r="C45" s="6">
-        <v>0</v>
-      </c>
-      <c r="D45" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="46" spans="1:4" ht="64" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
@@ -1392,21 +1679,25 @@
         <v>68</v>
       </c>
       <c r="C46" s="6">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7"/>
+        <v>-1</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="47" spans="1:4" ht="160" x14ac:dyDescent="0.2">
-      <c r="A47" s="8">
+      <c r="A47" s="7">
         <v>46</v>
       </c>
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="8" t="s">
         <v>69</v>
       </c>
       <c r="C47" s="6">
         <v>-1</v>
       </c>
-      <c r="D47" s="10"/>
+      <c r="D47" s="9" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="48" spans="1:4" ht="48" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
@@ -1416,21 +1707,25 @@
         <v>70</v>
       </c>
       <c r="C48" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D48" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="49" spans="1:4" ht="192" x14ac:dyDescent="0.2">
-      <c r="A49" s="8">
+      <c r="A49" s="7">
         <v>48</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="8" t="s">
         <v>71</v>
       </c>
       <c r="C49" s="6">
         <v>1</v>
       </c>
-      <c r="D49" s="10"/>
+      <c r="D49" s="9" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="50" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
@@ -1442,19 +1737,23 @@
       <c r="C50" s="6">
         <v>0</v>
       </c>
-      <c r="D50" s="7"/>
+      <c r="D50" s="10" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="51" spans="1:4" ht="144" x14ac:dyDescent="0.2">
-      <c r="A51" s="8">
+      <c r="A51" s="7">
         <v>50</v>
       </c>
-      <c r="B51" s="9" t="s">
+      <c r="B51" s="8" t="s">
         <v>73</v>
       </c>
       <c r="C51" s="6">
         <v>1</v>
       </c>
-      <c r="D51" s="10"/>
+      <c r="D51" s="9" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="52" spans="1:4" ht="144" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
@@ -1466,19 +1765,23 @@
       <c r="C52" s="6">
         <v>1</v>
       </c>
-      <c r="D52" s="7"/>
+      <c r="D52" s="10" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="53" spans="1:4" ht="288" x14ac:dyDescent="0.2">
-      <c r="A53" s="8">
+      <c r="A53" s="7">
         <v>52</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="B53" s="8" t="s">
         <v>75</v>
       </c>
       <c r="C53" s="6">
         <v>-1</v>
       </c>
-      <c r="D53" s="10"/>
+      <c r="D53" s="9" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="54" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
@@ -1490,19 +1793,23 @@
       <c r="C54" s="6">
         <v>1</v>
       </c>
-      <c r="D54" s="7"/>
+      <c r="D54" s="10" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="55" spans="1:4" ht="144" x14ac:dyDescent="0.2">
-      <c r="A55" s="8">
+      <c r="A55" s="7">
         <v>54</v>
       </c>
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="8" t="s">
         <v>77</v>
       </c>
       <c r="C55" s="6">
-        <v>0</v>
-      </c>
-      <c r="D55" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="56" spans="1:4" ht="96" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
@@ -1514,19 +1821,23 @@
       <c r="C56" s="6">
         <v>1</v>
       </c>
-      <c r="D56" s="7"/>
+      <c r="D56" s="10" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="57" spans="1:4" ht="96" x14ac:dyDescent="0.2">
-      <c r="A57" s="8">
+      <c r="A57" s="7">
         <v>56</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="8" t="s">
         <v>79</v>
       </c>
       <c r="C57" s="6">
-        <v>1</v>
-      </c>
-      <c r="D57" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="58" spans="1:4" ht="112" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
@@ -1536,21 +1847,25 @@
         <v>80</v>
       </c>
       <c r="C58" s="6">
-        <v>1</v>
-      </c>
-      <c r="D58" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="59" spans="1:4" ht="128" x14ac:dyDescent="0.2">
-      <c r="A59" s="8">
+      <c r="A59" s="7">
         <v>58</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="8" t="s">
         <v>81</v>
       </c>
       <c r="C59" s="6">
         <v>-1</v>
       </c>
-      <c r="D59" s="10"/>
+      <c r="D59" s="9" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="60" spans="1:4" ht="192" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
@@ -1560,21 +1875,25 @@
         <v>82</v>
       </c>
       <c r="C60" s="6">
-        <v>0</v>
-      </c>
-      <c r="D60" s="7"/>
+        <v>1</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="61" spans="1:4" ht="112" x14ac:dyDescent="0.2">
-      <c r="A61" s="8">
+      <c r="A61" s="7">
         <v>60</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="8" t="s">
         <v>83</v>
       </c>
       <c r="C61" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D61" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="62" spans="1:4" ht="128" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
@@ -1584,21 +1903,25 @@
         <v>84</v>
       </c>
       <c r="C62" s="6">
-        <v>1</v>
-      </c>
-      <c r="D62" s="7"/>
+        <v>-1</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="63" spans="1:4" ht="128" x14ac:dyDescent="0.2">
-      <c r="A63" s="8">
+      <c r="A63" s="7">
         <v>62</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="8" t="s">
         <v>85</v>
       </c>
       <c r="C63" s="6">
         <v>0</v>
       </c>
-      <c r="D63" s="10"/>
+      <c r="D63" s="9" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="64" spans="1:4" ht="320" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
@@ -1608,21 +1931,25 @@
         <v>86</v>
       </c>
       <c r="C64" s="6">
-        <v>1</v>
-      </c>
-      <c r="D64" s="7"/>
+        <v>-1</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="65" spans="1:4" ht="208" x14ac:dyDescent="0.2">
-      <c r="A65" s="8">
+      <c r="A65" s="7">
         <v>64</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="8" t="s">
         <v>87</v>
       </c>
       <c r="C65" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D65" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="66" spans="1:4" ht="128" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
@@ -1634,19 +1961,23 @@
       <c r="C66" s="6">
         <v>-1</v>
       </c>
-      <c r="D66" s="7"/>
+      <c r="D66" s="10" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="67" spans="1:4" ht="160" x14ac:dyDescent="0.2">
-      <c r="A67" s="8">
+      <c r="A67" s="7">
         <v>66</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="8" t="s">
         <v>89</v>
       </c>
       <c r="C67" s="6">
-        <v>1</v>
-      </c>
-      <c r="D67" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="68" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
@@ -1656,21 +1987,25 @@
         <v>90</v>
       </c>
       <c r="C68" s="6">
-        <v>0</v>
-      </c>
-      <c r="D68" s="7"/>
+        <v>-1</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="69" spans="1:4" ht="64" x14ac:dyDescent="0.2">
-      <c r="A69" s="8">
+      <c r="A69" s="7">
         <v>68</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="8" t="s">
         <v>91</v>
       </c>
       <c r="C69" s="6">
         <v>1</v>
       </c>
-      <c r="D69" s="10"/>
+      <c r="D69" s="9" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="70" spans="1:4" ht="176" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
@@ -1680,21 +2015,23 @@
         <v>92</v>
       </c>
       <c r="C70" s="6">
-        <v>1</v>
-      </c>
-      <c r="D70" s="7"/>
+        <v>-1</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="71" spans="1:4" ht="96" x14ac:dyDescent="0.2">
-      <c r="A71" s="8">
+      <c r="A71" s="7">
         <v>70</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="8" t="s">
         <v>93</v>
       </c>
       <c r="C71" s="6">
-        <v>-1</v>
-      </c>
-      <c r="D71" s="10"/>
+        <v>0</v>
+      </c>
+      <c r="D71" s="9"/>
     </row>
     <row r="72" spans="1:4" ht="350" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
@@ -1706,19 +2043,19 @@
       <c r="C72" s="6">
         <v>-1</v>
       </c>
-      <c r="D72" s="7"/>
+      <c r="D72" s="10"/>
     </row>
     <row r="73" spans="1:4" ht="80" x14ac:dyDescent="0.2">
-      <c r="A73" s="8">
+      <c r="A73" s="7">
         <v>72</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="8" t="s">
         <v>95</v>
       </c>
       <c r="C73" s="6">
         <v>1</v>
       </c>
-      <c r="D73" s="10"/>
+      <c r="D73" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/signal/validation/paragraphs_to_label.xlsx
+++ b/signal/validation/paragraphs_to_label.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1AA6033-8104-B049-B235-5731782F0AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="16080" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
